--- a/Configs/GameConfig/Datas/chapterItem.xlsx
+++ b/Configs/GameConfig/Datas/chapterItem.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Git\TEngine_main\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD5C796-8A2D-4136-A0AC-12F7CC27F86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139E6F91-984C-4910-B97B-2C48D5BAFF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,12 +136,40 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>location</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level_list</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,0;2,200;3,400;4,600;5,800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=;),chapter.ChapterItemLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级列表(等级+价格)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +197,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -190,9 +225,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -473,16 +509,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,8 +530,14 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -503,63 +547,96 @@
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="21.75" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>101</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>102</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B9" s="1">
         <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" s="1">
         <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="1">
         <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
